--- a/balance_tables/特殊强化.xlsx
+++ b/balance_tables/特殊强化.xlsx
@@ -1346,7 +1346,7 @@
       </c>
       <c r="H7" s="26" t="inlineStr">
         <is>
-          <t>每3秒额外发射一根横跨四格、滚动直行的巨型法棍</t>
+          <t>以3秒基础间隔额外发射一根横跨四格、滚动直行的巨型法棍</t>
         </is>
       </c>
       <c r="I7" s="26" t="n"/>
@@ -1443,7 +1443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1542,7 +1542,7 @@
         </is>
       </c>
       <c r="B5" s="30" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
@@ -1552,106 +1552,6 @@
       <c r="D5" s="3" t="inlineStr">
         <is>
           <t>按倍率的等级次方计算</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>baguette_giant_interval_seconds</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>3</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>巨型法棍的固定发射间隔（秒）</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>不受快速备餐影响</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>baguette_giant_width_regions</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>4</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>巨型法棍横跨的道路格数</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>改变模型长度与横向命中范围</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>baguette_giant_pierce_count</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>999</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>每根巨型法棍最多命中的不同目标数</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>独立于法棍基础穿透和酱油</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>baguette_giant_duration_multiplier</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>相对法棍当前持续时间的倍率</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>会继续继承淀粉的持续加成</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>baguette_giant_satisfaction_multiplier</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>3</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>相对法棍当前满足值的倍率</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>会继承法棍等级和糖的满足加成</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1632,7 @@
       </c>
       <c r="B5" s="32" t="inlineStr">
         <is>
-          <t>呼吸菌圈参数来自武器.xlsx；巨型法棍的间隔、宽度、穿透和倍率来自本表“全局规则”。</t>
+          <t>呼吸菌圈与巨型法棍的攻击参数均来自武器.xlsx；本表只负责解锁对应进化。</t>
         </is>
       </c>
     </row>

--- a/balance_tables/特殊强化.xlsx
+++ b/balance_tables/特殊强化.xlsx
@@ -365,7 +365,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SpecialUpgradeTable" displayName="SpecialUpgradeTable" ref="A1:I11" headerRowCount="1" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SpecialUpgradeTable" displayName="SpecialUpgradeTable" ref="A1:I12" headerRowCount="1" totalsRowShown="0">
   <tableColumns count="9">
     <tableColumn id="1" name="强化ID"/>
     <tableColumn id="2" name="显示名称"/>
@@ -1367,7 +1367,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8"/>
   <cols>
     <col width="22" customWidth="1" style="32" min="1" max="1"/>
@@ -1806,6 +1806,42 @@
       <c r="I11" t="inlineStr">
         <is>
           <t>提高自身基础满足值</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>carrot_bounce</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>往返扫掠</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>evolution</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>carrot</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="b">
+        <v>0</v>
+      </c>
+      <c r="G12" t="b">
+        <v>1</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>胡萝卜扫到端点后反向往返</t>
         </is>
       </c>
     </row>
